--- a/sent_log.xlsx
+++ b/sent_log.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -915,10 +915,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>10:06:07</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>727911</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -935,6 +951,168 @@
           <t>FRndz GRN</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>10:22:16</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>727896</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>12:23:44</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>727616</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>10:22:59</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>727923</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>12:40:11</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>727960</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>10:23:45</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>727941</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>10:27:26</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>727907</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>16:17:41</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>728081</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sent_log.xlsx
+++ b/sent_log.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1057,10 +1057,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>18:28:16</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>728574</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1083,10 +1099,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>18:33:21</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>728586</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1109,10 +1141,262 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>18:35:45</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>728595</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>18:18:09</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>728476</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>18:58:25</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>728598</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>18:18:36</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>728661</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>18:59:06</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>728547</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>18:19:52</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>728711</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>19:12:50</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>728687</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>18:23:42</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>728532</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>19:13:03</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>728534</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>19:19:23</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>728651</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>19:19:39</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>728518</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>19:21:22</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>728656</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sent_log.xlsx
+++ b/sent_log.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1393,10 +1393,1322 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>18:53:26</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>731138</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>11:01:55</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>732812</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>10:00:26</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>730070</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>11:16:25</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>732576</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>10:15:55</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>733070</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>11:21:50</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>732731</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>11:07:12</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>732843</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>11:25:11</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>732654</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>16:48:27</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>733097</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>11:25:26</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>732728</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>16:49:50</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>733136</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>11:43:16</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>732828</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>16:56:50</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>733146</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>12:12:18</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>732758</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>16:58:43</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>733104</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>15:46:07</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>732791</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>14:46:37</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>733485</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>15:47:15</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>732848</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>14:48:21</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>733518</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>15:48:58</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>732931</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>15:46:07</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>733380</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>15:55:01</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>732898</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>15:24:05</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>733742</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>15:55:27</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>732960</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>15:24:35</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>733957</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>16:45:13</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>732932</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>17:06:26</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>734741</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>17:26:50</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>732972</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>19:28:08</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>734876</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>17:39:36</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>732977</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>19:30:44</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>734736</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>09:52:38</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>733064</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>19:50:29</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>734803</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>10:12:48</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>732984</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>10:13:31</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>733111</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>10:17:36</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>733109</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>10:22:25</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>733092</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>10:53:21</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>733064</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>11:00:38</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>733109</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>11:02:14</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>733070</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>11:06:58</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>732843</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>12:33:29</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>733076</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>13:14:13</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>733071</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>13:30:14</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>733149</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>13:55:11</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>733211</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>14:43:25</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>732807</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>16:07:16</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>733537</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>16:51:49</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>733385</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>11:23:33</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>733974</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>11:27:44</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>734071</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>17:59:30</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>734933</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>18:11:38</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>734886</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>19:01:29</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>734795</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>19:07:54</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>734878</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>19:23:00</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>734824</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>19:24:16</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>734824</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>19:25:59</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>734957</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sent_log.xlsx
+++ b/sent_log.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2107,10 +2107,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>13:31:04</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>736174</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2133,10 +2149,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>13:41:00</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>736168</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2159,10 +2191,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>14:22:15</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>736025</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2185,10 +2233,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>11:13:40</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>736550</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2211,10 +2275,26 @@
           <t>EGF GDN</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>12:14:10</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>736414</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>EGF GRN</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2710,6 +2790,370 @@
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>00:46:32</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>734972</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>01:47:22</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>734911</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>KFC GDN</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>01:50:12</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>734955</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>02:48:07</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>734923</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>01:03:33</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>735787</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>12:01:49</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>736163</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>12:02:05</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>736153</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>13:10:47</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>736157</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>11:42:13</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>737112</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>12:07:50</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>737134</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>14:13:01</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>737118</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>14:15:47</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>737181</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>14:24:23</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>737180</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>16:11:45</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>737240</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>EGF GDN</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
